--- a/output/pdf_financials_xlsx/EOM.xlsx
+++ b/output/pdf_financials_xlsx/EOM.xlsx
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.289</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.207</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>2.642</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.289</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.207</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>2.642</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.388</v>
+        <v>0.099</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.28</v>
+        <v>0.073</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.789</v>
+        <v>0.147</v>
       </c>
     </row>
     <row r="49">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/EOM.xlsx
+++ b/output/pdf_financials_xlsx/EOM.xlsx
@@ -2221,13 +2221,13 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.188</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.126</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.183</v>
       </c>
     </row>
     <row r="113">
@@ -4093,7 +4093,11 @@
           <t>Proceeds from disposal of plant and equipment 3</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E48" s="5" t="n">
         <v>0.188</v>
       </c>

--- a/output/pdf_financials_xlsx/EOM.xlsx
+++ b/output/pdf_financials_xlsx/EOM.xlsx
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.098</v>
+        <v>0.328</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.037</v>
+        <v>0.246</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.01</v>
+        <v>0.211</v>
       </c>
     </row>
     <row r="8">
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.747</v>
+        <v>0.977</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.154</v>
+        <v>0.363</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.239</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.747</v>
+        <v>-0.977</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.154</v>
+        <v>-0.363</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.239</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="12">
@@ -1510,13 +1510,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.919</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.574</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="68">
@@ -1526,13 +1526,13 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>1.217</v>
+        <v>2.136</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>1.071</v>
+        <v>1.645</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0.471</v>
+        <v>0.521</v>
       </c>
     </row>
     <row r="69">
@@ -1644,7 +1644,7 @@
         <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.216</v>
+        <v>0.166</v>
       </c>
     </row>
     <row r="76">
@@ -3644,7 +3644,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -5354,17 +5358,21 @@
           <t>Management and directors' fees 11</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F89" s="5" t="n">
-        <v>-0.209</v>
+        <v>0.209</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>-0.201</v>
+        <v>0.201</v>
       </c>
     </row>
     <row r="90">
@@ -6117,12 +6125,16 @@
           <t>Management and directors' fees 12</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E114" s="5" t="n">
-        <v>-0.23</v>
+        <v>0.23</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>-0.209</v>
+        <v>0.209</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
